--- a/output/lmm_summary.xlsx
+++ b/output/lmm_summary.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,32 +467,46 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>STAGE[T.LATE]</t>
         </is>
       </c>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Group Var</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Group x MONTH Cov</t>
+          <t>MONTH:STAGE[T.LATE]</t>
         </is>
       </c>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>MONTH Var</t>
+          <t>Group Var</t>
         </is>
       </c>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Group x MONTH Cov</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MONTH Var</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -571,6 +585,36 @@
           <t>pval_fdr</t>
         </is>
       </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>pval_fdr</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>pval_fdr</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -579,7 +623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.94</v>
+        <v>21.449</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -588,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>14.774</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.022</v>
+        <v>0.177</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -606,21 +650,39 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.006</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -631,7 +693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.308</v>
+        <v>4.209</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -640,17 +702,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>2.128</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.027</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.434</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -658,21 +720,39 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.001</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.511</v>
+        <v>9.875</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -692,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.076</v>
+        <v>5.433</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -701,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.844</v>
+        <v>0.079</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -710,21 +790,39 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.006</v>
+        <v>-0.016</v>
       </c>
       <c r="L6" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.723</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.004</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -735,7 +833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.655</v>
+        <v>1.207</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -744,17 +842,17 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>5.008</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.041</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.794</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -762,21 +860,39 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="N7" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.001</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -787,7 +903,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.665</v>
+        <v>4.525</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -796,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.015</v>
+        <v>1.088</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="H8" t="n">
-        <v>2.342</v>
+        <v>0.017</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -814,29 +930,49 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.337</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.008</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>

--- a/output/lmm_summary.xlsx
+++ b/output/lmm_summary.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.449</v>
+        <v>11.855</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>14.774</v>
+        <v>12.409</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.177</v>
+        <v>0.205</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.067</v>
+        <v>-0.142</v>
       </c>
       <c r="L4" t="n">
-        <v>0.062</v>
+        <v>0.023</v>
       </c>
       <c r="M4" t="n">
-        <v>0.148</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="N4" t="n">
-        <v>1.805</v>
+        <v>1.862</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -668,16 +668,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.012</v>
+        <v>0.7087499999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.209</v>
+        <v>1.922</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.128</v>
+        <v>2.408</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.014</v>
+        <v>-0.023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.089</v>
+        <v>0.187</v>
       </c>
       <c r="M5" t="n">
-        <v>0.148</v>
+        <v>0.192</v>
       </c>
       <c r="N5" t="n">
-        <v>1.417</v>
+        <v>2.221</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -738,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.001</v>
+        <v>-0.027</v>
       </c>
       <c r="R5" t="n">
-        <v>0.627</v>
+        <v>0.013</v>
       </c>
       <c r="S5" t="n">
-        <v>0.627</v>
+        <v>0.03249999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.875</v>
+        <v>5.011</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5.433</v>
+        <v>6.715</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.079</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.016</v>
+        <v>-0.081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.387</v>
+        <v>0.025</v>
       </c>
       <c r="M6" t="n">
-        <v>0.484</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>1.723</v>
+        <v>1.977</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -808,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.005</v>
+        <v>-0.024</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004</v>
+        <v>0.024</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.207</v>
+        <v>1.035</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>5.008</v>
+        <v>0.904</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -851,25 +851,25 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.003</v>
+        <v>0.014</v>
       </c>
       <c r="L7" t="n">
-        <v>0.708</v>
+        <v>0.192</v>
       </c>
       <c r="M7" t="n">
-        <v>0.708</v>
+        <v>0.192</v>
       </c>
       <c r="N7" t="n">
-        <v>1.148</v>
+        <v>1.725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -878,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.001</v>
+        <v>0.032</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.525</v>
+        <v>2.942</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -912,34 +912,34 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.088</v>
+        <v>1.386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.026</v>
+        <v>-0.045</v>
       </c>
       <c r="L8" t="n">
-        <v>0.027</v>
+        <v>0.014</v>
       </c>
       <c r="M8" t="n">
-        <v>0.135</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>2.337</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -948,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.008</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001</v>
+        <v>0.969</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005</v>
+        <v>0.969</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>

--- a/output/lmm_summary.xlsx
+++ b/output/lmm_summary.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.855</v>
+        <v>7.21</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12.409</v>
+        <v>17.556</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.205</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.142</v>
+        <v>0.093</v>
       </c>
       <c r="L4" t="n">
-        <v>0.023</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.0225</v>
       </c>
       <c r="N4" t="n">
-        <v>1.862</v>
+        <v>3.149</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -668,16 +668,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.005</v>
+        <v>0.056</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7087499999999999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.922</v>
+        <v>1.19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.408</v>
+        <v>3.18</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.044</v>
+        <v>0.026</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.023</v>
+        <v>0.019</v>
       </c>
       <c r="L5" t="n">
-        <v>0.187</v>
+        <v>0.066</v>
       </c>
       <c r="M5" t="n">
-        <v>0.192</v>
+        <v>0.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.221</v>
+        <v>2.018</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -738,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.027</v>
+        <v>0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03249999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.011</v>
+        <v>2.972</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6.715</v>
+        <v>8.843</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.081</v>
+        <v>0.033</v>
       </c>
       <c r="L6" t="n">
-        <v>0.025</v>
+        <v>0.105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.13125</v>
       </c>
       <c r="N6" t="n">
-        <v>1.977</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -808,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.024</v>
+        <v>0.013</v>
       </c>
       <c r="R6" t="n">
-        <v>0.024</v>
+        <v>0.105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04</v>
+        <v>0.105</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.035</v>
+        <v>0.656</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.904</v>
+        <v>1.104</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -851,25 +851,25 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.027</v>
+        <v>0.017</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.001</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.192</v>
-      </c>
       <c r="M7" t="n">
-        <v>0.192</v>
+        <v>0.005</v>
       </c>
       <c r="N7" t="n">
-        <v>1.725</v>
+        <v>1.619</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -878,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.942</v>
+        <v>1.851</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.386</v>
+        <v>3.129</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -921,43 +921,43 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.127</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.045</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.04166666666666667</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.969</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.969</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>

--- a/output/lmm_summary.xlsx
+++ b/output/lmm_summary.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.21</v>
+        <v>7.457</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>17.556</v>
+        <v>17.815</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.117</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.093</v>
+        <v>0.065</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0225</v>
+        <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>3.149</v>
+        <v>3.262</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.056</v>
+        <v>0.022</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.19</v>
+        <v>1.214</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3.18</v>
+        <v>3.276</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,34 +720,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.019</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.018</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.972</v>
+        <v>3.1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.843</v>
+        <v>8.904</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.066</v>
+        <v>0.049</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.105</v>
+        <v>0.027</v>
       </c>
       <c r="M6" t="n">
-        <v>0.13125</v>
+        <v>0.03375</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.484</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -808,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.105</v>
+        <v>0.776</v>
       </c>
       <c r="S6" t="n">
-        <v>0.105</v>
+        <v>0.776</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.656</v>
+        <v>0.665</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.104</v>
+        <v>1.263</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -851,25 +851,25 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.017</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.022</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.619</v>
+        <v>1.771</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -878,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="R7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.004</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.006</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.851</v>
+        <v>1.937</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3.129</v>
+        <v>3.009</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -930,16 +930,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="L8" t="n">
-        <v>0.873</v>
+        <v>0.454</v>
       </c>
       <c r="M8" t="n">
-        <v>0.873</v>
+        <v>0.454</v>
       </c>
       <c r="N8" t="n">
-        <v>3.127</v>
+        <v>3.365</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -948,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.045</v>
+        <v>0.006</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="T8" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>

--- a/output/lmm_summary.xlsx
+++ b/output/lmm_summary.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.457</v>
+        <v>14.66</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>17.815</v>
+        <v>10.612</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.117</v>
+        <v>0.239</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.065</v>
+        <v>-0.058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="N4" t="n">
-        <v>3.262</v>
+        <v>2.063</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -668,13 +668,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.022</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="T4" t="n">
         <v>0.004</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.214</v>
+        <v>2.492</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3.276</v>
+        <v>1.995</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.022</v>
+        <v>0.048</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.016</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003</v>
+        <v>0.239</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005</v>
+        <v>0.239</v>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>2.027</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1</v>
+        <v>6.014</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.904</v>
+        <v>5.966</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.049</v>
+        <v>0.105</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.027</v>
+        <v>-0.028</v>
       </c>
       <c r="L6" t="n">
-        <v>0.027</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03375</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>2.484</v>
+        <v>2.329</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -808,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001</v>
+        <v>0.018</v>
       </c>
       <c r="R6" t="n">
-        <v>0.776</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.776</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.665</v>
+        <v>1.155</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.263</v>
+        <v>0.772</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.016</v>
+        <v>0.024</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -860,16 +860,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="N7" t="n">
-        <v>1.771</v>
+        <v>1.701</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -878,13 +878,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="S7" t="n">
-        <v>0.015</v>
+        <v>0.4500000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>0.004</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.937</v>
+        <v>3.863</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3.009</v>
+        <v>1.085</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -930,16 +930,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.005</v>
+        <v>-0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>0.454</v>
+        <v>0.006</v>
       </c>
       <c r="M8" t="n">
-        <v>0.454</v>
+        <v>0.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.365</v>
+        <v>2.886</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="R8" t="n">
-        <v>0.168</v>
+        <v>0.649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.21</v>
+        <v>0.81125</v>
       </c>
       <c r="T8" t="n">
         <v>0.003</v>
